--- a/data/Issued_vs_Not_Issued.xlsx
+++ b/data/Issued_vs_Not_Issued.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,78 +456,78 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ART0131</t>
+          <t>ART0102</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Democratic Republic of Congo Mai-Ndombe FCPF Emission Reductions Program</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CD</t>
+          <t>GY</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1669630</v>
+        <v>62003028</v>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2020-12-21</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2018-09-21</t>
+          <t>2016-01-01</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ART0130</t>
+          <t>ART0131</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cote d'Ivoire Tai National Park Area Emission Reductions Program</t>
+          <t>Democratic Republic of Congo Mai-Ndombe FCPF Emission Reductions Program</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>429590</v>
+        <v>1669630</v>
       </c>
       <c r="E3" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2019-01-01</t>
+          <t>2018-09-21</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ART0126</t>
+          <t>ART0101</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Costa Rica FCPF REDD+ Emission Reductions Program</t>
+          <t>Costa Rica</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -536,201 +536,201 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>100000</v>
+        <v>1171032</v>
       </c>
       <c r="E4" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2020-12-21</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2018-01-01</t>
+          <t>2017-01-01</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ART0111</t>
+          <t>ART0130</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>Cote d'Ivoire Tai National Park Area Emission Reductions Program</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>429590</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2021-12-31</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2017-01-01</t>
+          <t>2019-01-01</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ART0112</t>
+          <t>ART0126</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DRC Province of Tshuapa</t>
+          <t>Costa Rica FCPF REDD+ Emission Reductions Program</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CD</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2022-01-13</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2017-01-01</t>
+          <t>2018-01-01</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ART0113</t>
+          <t>ART0103</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Tocantins</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NP</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2022-02-09</t>
+          <t>2020-12-23</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2022-01-01</t>
+          <t>2020-01-01</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ART0114</t>
+          <t>ART0104</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Gabon</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2022-04-13</t>
+          <t>2020-12-30</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2018-01-01</t>
+          <t>2016-01-01</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ART0115</t>
+          <t>ART0105</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Quintana Roo</t>
+          <t>Amapá</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
+          <t>2020-12-30</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2022-01-01</t>
+          <t>2016-01-01</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ART0116</t>
+          <t>ART0106</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ET</t>
+          <t>GH</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -741,29 +741,29 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2023-01-12</t>
+          <t>2021-08-10</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2018-01-01</t>
+          <t>2017-01-01</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ART0118</t>
+          <t>ART0107</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>Viet Nam</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>VN</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -774,62 +774,62 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2023-01-31</t>
+          <t>2021-08-11</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2018-01-01</t>
+          <t>2021-01-01</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ART0119</t>
+          <t>ART0108</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Jalisco REDD+ Program</t>
+          <t>Amazon Region</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2023-07-10</t>
+          <t>2021-11-01</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2022-01-01</t>
+          <t>2021-01-01</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ART0120</t>
+          <t>ART0109</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mato Grosso REDD+ Program</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -840,274 +840,604 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2023-12-09</t>
+          <t>2021-11-18</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>2017-01-01</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ART0121</t>
+          <t>ART0110</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Burkina Faso REDD+ Program</t>
+          <t>Papua New Guinea</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BF</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2023-12-21</t>
+          <t>2021-12-31</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2017-01-01</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ART0123</t>
+          <t>ART0111</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Acre</t>
+          <t>Peru</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2021-12-31</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2023-01-01</t>
+          <t>2017-01-01</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ART0124</t>
+          <t>ART0112</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Para REDD+ Program</t>
+          <t>DRC Province of Tshuapa</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2022-01-13</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2023-01-01</t>
+          <t>2017-01-01</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ART0125</t>
+          <t>ART0113</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Indigenous Jurisdictional REDD+ Program</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>NP</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2022-02-09</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2021-01-01</t>
+          <t>2022-01-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ART0127</t>
+          <t>ART0114</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Yucatan REDD+ Program</t>
+          <t>Gabon</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2022-04-13</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>2018-01-01</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ART0128</t>
+          <t>ART0115</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bhutan REDD+ Program</t>
+          <t>Quintana Roo</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BT</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2020-01-01</t>
+          <t>2022-01-01</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ART0129</t>
+          <t>ART0116</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bolivia's REDD+ Program in Charagua</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>BO</t>
+          <t>ET</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2023-01-12</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2023-01-01</t>
+          <t>2018-01-01</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>ART0118</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Uganda</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2023-01-31</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2018-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ART0119</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Jalisco REDD+ Program</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>MX</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2023-07-10</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ART0120</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Mato Grosso REDD+ Program</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2023-12-09</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ART0121</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Burkina Faso REDD+ Program</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>BF</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2023-12-21</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ART0123</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Acre</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ART0124</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Para REDD+ Program</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>6</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2024-10-28</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ART0125</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Indigenous Jurisdictional REDD+ Program</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>3</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2024-11-07</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2021-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ART0127</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Yucatan REDD+ Program</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>MX</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2024-12-12</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ART0128</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Bhutan REDD+ Program</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>BT</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>3</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2020-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ART0129</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Bolivia's REDD+ Program in Charagua</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>ART0132</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Central African Republic REDD+ Program</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>CF</t>
         </is>
       </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>4</v>
-      </c>
-      <c r="F21" t="inlineStr">
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>2024-01-01</t>
         </is>
